--- a/docs/import/bets-sample.xlsx
+++ b/docs/import/bets-sample.xlsx
@@ -172,7 +172,7 @@
     <t>status</t>
   </si>
   <si>
-    <t>open</t>
+    <t>closed</t>
   </si>
   <si>
     <t>result</t>
